--- a/exports/registros_semanais.xlsx
+++ b/exports/registros_semanais.xlsx
@@ -84,12 +84,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -457,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -616,7 +619,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>43</v>
@@ -646,8 +649,16 @@
           <t>Chuva Parcial</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Chuva Parcial</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Chuva Produtiva</t>
+        </is>
+      </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
           <t>2026-06-09 12:19:24</t>
@@ -655,7 +666,96 @@
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09 12:19:24</t>
+          <t>2026-06-10 15:37:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>00f1a29c-b150-41a0-a15a-9be1ef321b59</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>y6456</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>gabriel</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>rsthesth</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>etyesty</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>5454</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Chuva Parcial</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Tempo Bom</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Tempo Bom</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Tempo Bom</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>Tempo Bom</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>Sem Expediente</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>Sem Expediente</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-10 16:11:59</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-10 16:11:59</t>
         </is>
       </c>
     </row>
@@ -670,7 +770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -713,6 +813,66 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>00f1a29c-b150-41a0-a15a-9be1ef321b59</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>gabriel</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Mestre de Obras</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>direto</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>00f1a29c-b150-41a0-a15a-9be1ef321b59</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>gabriel</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Eletricista</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>direto</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -724,7 +884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -761,6 +921,56 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>00f1a29c-b150-41a0-a15a-9be1ef321b59</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>gabriel</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Guindaste sobre Esteiras</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>00f1a29c-b150-41a0-a15a-9be1ef321b59</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>gabriel</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Rolo Compactador Pé de Carneiro</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/exports/registros_semanais.xlsx
+++ b/exports/registros_semanais.xlsx
@@ -18,7 +18,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="&quot;R$&quot; #,##0.00"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;%&quot;"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -84,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -92,7 +95,19 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -460,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:T6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -473,15 +488,16 @@
     <col width="35" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="35" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
     <col width="18" customWidth="1" min="15" max="15"/>
     <col width="18" customWidth="1" min="16" max="16"/>
     <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
+    <col width="20" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -537,45 +553,50 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>Ações Realizadas</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Pluv. Segunda</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Pluv. Terça</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Pluv. Quarta</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Pluv. Quinta</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Pluv. Sexta</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Pluv. Sábado</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Pluv. Domingo</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Criado Em</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Atualizado Em</t>
         </is>
@@ -584,178 +605,454 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>e278aac5-2e07-4291-8ede-9b7b52483a73</t>
+          <t>a1b2c3d4-0001-4001-8001-100000000001</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>45645</t>
+          <t>CT-2024-001</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Engenharia Beta</t>
+          <t>Construtora Alpha</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Início da concretagem dos pilares do bloco A. Mobilização de equipe de alvenaria.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Solo com umidade elevada na área do bloco B — aguardar condições para fundação.</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>45000</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Tempo Bom</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Tempo Bom</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Chuva Parcial</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Tempo Bom</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Tempo Bom</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Sem Expediente</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>Sem Expediente</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15 09:30:00</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-15 09:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>a1b2c3d4-0001-4001-8001-100000000002</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>CT-2024-001</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Construtora Alpha</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Concretagem dos pilares P1 a P8 concluída. Início da alvenaria de vedação bloco A.</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Aguardar entrega de blocos cerâmicos prevista para próxima semana.</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="n">
+        <v>52000</v>
+      </c>
+      <c r="J3" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="K3" s="5" t="inlineStr"/>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>Tempo Bom</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>Tempo Bom</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Tempo Bom</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>Chuva Produtiva</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>Tempo Bom</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>Sem Expediente</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>Sem Expediente</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:00:00</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-22 10:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>a1b2c3d4-0001-4001-8001-100000000003</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>CT-2024-001</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Construtora Alpha</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Alvenaria bloco A atingiu 3° pavimento. Concretagem da laje do 1° pavimento iniciada.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Verificar alinhamento das formas antes da concretagem da laje.</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>61000</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Tempo Bom</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Chuva Parcial</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Chuva Parcial</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>Tempo Bom</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Tempo Bom</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Chuva Produtiva</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>Sem Expediente</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29 11:15:00</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29 11:15:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>a1b2c3d4-0001-4001-8001-100000000004</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>CT-2024-001</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Construtora Alpha</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Laje do 1° pavimento concluída. Elevação da alvenaria do 2° pavimento em andamento.</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Chuva intensa na quarta-feira causou paralisação de 4 horas.</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>68000</v>
+      </c>
+      <c r="J5" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="K5" s="5" t="inlineStr"/>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>Tempo Bom</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>Tempo Bom</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>Chuva Improdutiva</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>Tempo Bom</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="inlineStr">
+        <is>
+          <t>Tempo Bom</t>
+        </is>
+      </c>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>Sem Expediente</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>Sem Expediente</t>
+        </is>
+      </c>
+      <c r="S5" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-05 09:45:00</t>
+        </is>
+      </c>
+      <c r="T5" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-05 09:45:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>a1b2c3d4-0001-4001-8001-100000000005</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>CT-2024-001</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Construtora Alpha</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>cvdc</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Alvenaria do 2° pavimento em ritmo acelerado. Preparação da armação para laje do 2° pavimento.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>bvfg</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>Chuva Produtiva</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>Chuva Produtiva</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>Incidência de Raio</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Nenhuma ocorrência relevante.</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Concretagem de Pilares: 15% | Alvenaria de Vedação: 50%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Tempo Bom</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Tempo Bom</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Tempo Bom</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>Tempo Bom</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>Chuva Parcial</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>Chuva Parcial</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>Chuva Parcial</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>Chuva Produtiva</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-09 12:19:24</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-10 15:37:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>00f1a29c-b150-41a0-a15a-9be1ef321b59</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>y6456</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>gabriel</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>rsthesth</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>etyesty</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>5454</v>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>Chuva Parcial</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>Tempo Bom</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>Tempo Bom</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>Tempo Bom</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>Tempo Bom</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>Sem Expediente</t>
         </is>
       </c>
-      <c r="Q3" s="3" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>Sem Expediente</t>
         </is>
       </c>
-      <c r="R3" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-10 16:11:59</t>
-        </is>
-      </c>
-      <c r="S3" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-10 16:11:59</t>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12 08:30:00</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12 17:57:12</t>
         </is>
       </c>
     </row>
@@ -770,7 +1067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -816,60 +1113,480 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>00f1a29c-b150-41a0-a15a-9be1ef321b59</t>
+          <t>a1b2c3d4-0001-4001-8001-100000000001</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>gabriel</t>
+          <t>Construtora Alpha</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>Pedreiro</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>direto</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>a1b2c3d4-0001-4001-8001-100000000001</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Construtora Alpha</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Servente</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>direto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>a1b2c3d4-0001-4001-8001-100000000001</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Construtora Alpha</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Encarregado</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>indireto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>a1b2c3d4-0001-4001-8001-100000000001</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Construtora Alpha</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
           <t>Mestre de Obras</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>indireto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>a1b2c3d4-0001-4001-8001-100000000002</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Construtora Alpha</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Pedreiro</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>direto</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>00f1a29c-b150-41a0-a15a-9be1ef321b59</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>gabriel</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Eletricista</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>a1b2c3d4-0001-4001-8001-100000000002</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Construtora Alpha</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Servente</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>direto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>a1b2c3d4-0001-4001-8001-100000000002</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Construtora Alpha</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Encarregado</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>indireto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>a1b2c3d4-0001-4001-8001-100000000002</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Construtora Alpha</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Mestre de Obras</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>indireto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>a1b2c3d4-0001-4001-8001-100000000003</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Construtora Alpha</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Pedreiro</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>direto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>a1b2c3d4-0001-4001-8001-100000000003</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Construtora Alpha</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Servente</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>direto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>a1b2c3d4-0001-4001-8001-100000000003</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Construtora Alpha</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Encarregado</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>indireto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>a1b2c3d4-0001-4001-8001-100000000003</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Construtora Alpha</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Mestre de Obras</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>indireto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>a1b2c3d4-0001-4001-8001-100000000004</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Construtora Alpha</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Pedreiro</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>direto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>a1b2c3d4-0001-4001-8001-100000000004</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Construtora Alpha</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Servente</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>direto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>a1b2c3d4-0001-4001-8001-100000000004</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Construtora Alpha</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Encarregado</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>indireto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>a1b2c3d4-0001-4001-8001-100000000004</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Construtora Alpha</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Mestre de Obras</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>indireto</t>
         </is>
       </c>
     </row>
@@ -884,7 +1601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -924,51 +1641,301 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>00f1a29c-b150-41a0-a15a-9be1ef321b59</t>
+          <t>a1b2c3d4-0001-4001-8001-100000000001</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>gabriel</t>
+          <t>Construtora Alpha</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>Betoneira</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>a1b2c3d4-0001-4001-8001-100000000001</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Construtora Alpha</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Andaime Tubular</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>a1b2c3d4-0001-4001-8001-100000000002</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Construtora Alpha</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Betoneira</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>a1b2c3d4-0001-4001-8001-100000000002</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Construtora Alpha</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Andaime Tubular</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>a1b2c3d4-0001-4001-8001-100000000002</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Construtora Alpha</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Caminhão Munck</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>a1b2c3d4-0001-4001-8001-100000000003</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Construtora Alpha</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Betoneira</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>a1b2c3d4-0001-4001-8001-100000000003</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Construtora Alpha</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Andaime Tubular</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>a1b2c3d4-0001-4001-8001-100000000003</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Construtora Alpha</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
           <t>Guindaste sobre Esteiras</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E9" s="5" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>00f1a29c-b150-41a0-a15a-9be1ef321b59</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>gabriel</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Rolo Compactador Pé de Carneiro</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>a1b2c3d4-0001-4001-8001-100000000004</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Construtora Alpha</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Betoneira</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>a1b2c3d4-0001-4001-8001-100000000004</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Construtora Alpha</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Andaime Tubular</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>a1b2c3d4-0001-4001-8001-100000000004</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Construtora Alpha</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Guindaste sobre Esteiras</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>a1b2c3d4-0001-4001-8001-100000000004</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Construtora Alpha</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Compactador de Placa</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
